--- a/output/2026-09-02_18_Italia_Molise_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-02_18_Italia_Molise_Impiantistica_aspirazione_industriale.xlsx
@@ -504,7 +504,7 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Forniture industriali generaliste con sezione dedicata aria compressa/vuototecnica e macchine per pulizia industriale (aspiratori, idropulitrici); offerta specifica su impiantistica di aspirazione da verificare a fondo.</t>
+          <t>Forniture industriali generaliste con sezione dedicata aria compressa/vuototecnica e macchine per pulizia industriale (aspiratori, idropulitrici); offerta specifica su impiantistica di aspirazione da verificare a fondo. [DUPLICATO — vedi anche: 2026-09-02_16_Italia_Molise_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Azienda attiva da 30+ anni, rivenditore di materiale/attrezzature termoidrauliche e impianti tecnologici per installatori/imprese; nessuna categoria 'aspirazione industriale' esplicita online, canale B2B affine da verificare.</t>
+          <t>Azienda attiva da 30+ anni, rivenditore di materiale/attrezzature termoidrauliche e impianti tecnologici per installatori/imprese; nessuna categoria 'aspirazione industriale' esplicita online, canale B2B affine da verificare. [DUPLICATO — vedi anche: 2026-09-02_16_Italia_Molise_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Sede legale fuori provincia (Montesilvano, PE), ma con pagina dedicata al servizio per la provincia di Isernia e vendita/noleggio di aspiratori industriali.</t>
+          <t>Sede legale fuori provincia (Montesilvano, PE), ma con pagina dedicata al servizio per la provincia di Isernia e vendita/noleggio di aspiratori industriali. [DUPLICATO — vedi anche: 2026-08-31_21_Italia_Liguria_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
